--- a/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_2778_completo.xlsx
+++ b/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_2778_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4a88498969304d7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5b6d921f49fb4767"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,156 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     93.5600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     85.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    100.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     93.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     93.1020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    101.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     98.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    103.5900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    101.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     91.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>13/08/2026</x:t>
         </x:is>
       </x:c>

--- a/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_2778_completo.xlsx
+++ b/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_2778_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5b6d921f49fb4767"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2e10cdca06b34b66"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,696 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     82.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     84.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     85.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     83.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.2800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     84.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     84.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     90.4100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     93.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     85.2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     89.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.7100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.3600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    106.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    107.4800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     93.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     94.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     96.2500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    101.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     96.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     96.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    102.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     94.5900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    100.7900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     98.9200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     96.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     98.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    141.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    105.9500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    101.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     99.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     98.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
